--- a/XLibur.Tests/Resource/Examples/Tables/ResizingTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Tables/ResizingTables.xlsx
@@ -501,186 +501,180 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:E13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.996339" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.424911" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.140625"/>
+    <x:col min="2" max="2" width="14.139196" customWidth="1"/>
+    <x:col min="3" max="3" width="11.996339" customWidth="1"/>
+    <x:col min="4" max="4" width="11.424911" customWidth="1"/>
+    <x:col min="5" max="5" width="9.710625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="D2" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="E2" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
-      <x:c r="B3" s="0">
+      <x:c r="B3">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="C3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="D3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E3" s="0">
+      <x:c r="E3">
         <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
-      <x:c r="B4" s="0">
+      <x:c r="B4">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="C4" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="D4" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E4" s="0">
+      <x:c r="E4">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
-      <x:c r="B5" s="0">
+      <x:c r="B5">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C5" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="D5" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E5" s="0">
+      <x:c r="E5">
         <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
-      <x:c r="B6" s="0">
+      <x:c r="B6">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
+      <x:c r="C6" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="D6" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E6" s="0">
+      <x:c r="E6">
         <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
-      <x:c r="B7" s="0">
+      <x:c r="B7">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
+      <x:c r="C7" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="D7" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E7" s="0">
+      <x:c r="E7">
         <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
-      <x:c r="B8" s="0">
+      <x:c r="B8">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
+      <x:c r="C8" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="D8" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="0">
+      <x:c r="E8">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
-      <x:c r="B9" s="0">
+      <x:c r="B9">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
+      <x:c r="C9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
+      <x:c r="D9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="0">
+      <x:c r="E9">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
-      <x:c r="B10" s="0">
+      <x:c r="B10">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C10" s="0" t="s">
+      <x:c r="C10" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D10" s="0" t="s">
+      <x:c r="D10" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E10" s="0">
+      <x:c r="E10">
         <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
-      <x:c r="B11" s="0">
+      <x:c r="B11">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C11" s="0" t="s">
+      <x:c r="C11" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D11" s="0" t="s">
+      <x:c r="D11" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E11" s="0">
+      <x:c r="E11">
         <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
-      <x:c r="B12" s="0">
+      <x:c r="B12">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
+      <x:c r="C12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D12" s="0" t="s">
+      <x:c r="D12" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E12" s="0">
+      <x:c r="E12">
         <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
-      <x:c r="B13" s="0" t="s">
+      <x:c r="B13" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E13" s="0">
+      <x:c r="E13">
         <x:f>SUBTOTAL(109,[Integer])</x:f>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -689,194 +683,181 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:E14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.996339" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.424911" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.140625"/>
+    <x:col min="2" max="2" width="14.139196" customWidth="1"/>
+    <x:col min="3" max="3" width="11.996339" customWidth="1"/>
+    <x:col min="4" max="4" width="11.424911" customWidth="1"/>
+    <x:col min="5" max="5" width="9.710625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="D2" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="E2" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
-      <x:c r="B3" s="0">
+      <x:c r="B3">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="C3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="D3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E3" s="0">
+      <x:c r="E3">
         <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
-      <x:c r="B4" s="0">
+      <x:c r="B4">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="C4" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="D4" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E4" s="0">
+      <x:c r="E4">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
-      <x:c r="B5" s="0">
+      <x:c r="B5">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C5" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="D5" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E5" s="0">
+      <x:c r="E5">
         <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
-      <x:c r="B6" s="0">
+      <x:c r="B6">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
+      <x:c r="C6" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="D6" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E6" s="0">
+      <x:c r="E6">
         <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
-      <x:c r="B7" s="0">
+      <x:c r="B7">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
+      <x:c r="C7" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="D7" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E7" s="0">
+      <x:c r="E7">
         <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
-      <x:c r="B8" s="0">
+      <x:c r="B8">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
+      <x:c r="C8" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="D8" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="0">
+      <x:c r="E8">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
-      <x:c r="B9" s="0">
+      <x:c r="B9">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
+      <x:c r="C9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
+      <x:c r="D9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="0">
+      <x:c r="E9">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
-      <x:c r="B10" s="0" t="s">
+      <x:c r="B10" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E10" s="0">
+      <x:c r="E10">
         <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
-      <x:c r="B11" s="0">
+      <x:c r="B11">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C11" s="0" t="s">
+      <x:c r="C11" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D11" s="0" t="s">
+      <x:c r="D11" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E11" s="0">
+      <x:c r="E11">
         <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
-      <x:c r="B12" s="0">
+      <x:c r="B12">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
+      <x:c r="C12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D12" s="0" t="s">
+      <x:c r="D12" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E12" s="0">
+      <x:c r="E12">
         <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
-      <x:c r="B13" s="0">
+      <x:c r="B13">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C13" s="0" t="s">
+      <x:c r="C13" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D13" s="0" t="s">
+      <x:c r="D13" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E13" s="0" t="e">
+      <x:c r="E13" t="e">
         <x:f>SUBTOTAL(109,[Integer])</x:f>
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
-    <x:oddHeader/>
-    <x:oddFooter/>
-    <x:evenHeader/>
-    <x:evenFooter/>
-    <x:firstHeader/>
-    <x:firstFooter/>
-  </x:headerFooter>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId9"/>
   </x:tableParts>
@@ -885,197 +866,184 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:E14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.282054" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.996339" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.424911" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11.282054" customWidth="1"/>
+    <x:col min="2" max="2" width="14.139196" customWidth="1"/>
+    <x:col min="3" max="3" width="11.996339" customWidth="1"/>
+    <x:col min="4" max="4" width="11.424911" customWidth="1"/>
+    <x:col min="5" max="5" width="9.710625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="D2" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="E2" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
-      <x:c r="B3" s="0">
+      <x:c r="B3">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="C3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="D3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E3" s="0">
+      <x:c r="E3">
         <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
-      <x:c r="B4" s="0">
+      <x:c r="B4">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="C4" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="D4" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E4" s="0">
+      <x:c r="E4">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
-      <x:c r="B5" s="0">
+      <x:c r="B5">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C5" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="D5" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E5" s="0">
+      <x:c r="E5">
         <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
-      <x:c r="B6" s="0">
+      <x:c r="B6">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
+      <x:c r="C6" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="D6" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E6" s="0">
+      <x:c r="E6">
         <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
-      <x:c r="B7" s="0">
+      <x:c r="B7">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
+      <x:c r="C7" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="D7" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E7" s="0">
+      <x:c r="E7">
         <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
-      <x:c r="B8" s="0">
+      <x:c r="B8">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
+      <x:c r="C8" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="D8" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="0">
+      <x:c r="E8">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
-      <x:c r="B9" s="0">
+      <x:c r="B9">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
+      <x:c r="C9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
+      <x:c r="D9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="0">
+      <x:c r="E9">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
-      <x:c r="B10" s="0">
+      <x:c r="B10">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C10" s="0" t="s">
+      <x:c r="C10" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D10" s="0" t="s">
+      <x:c r="D10" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E10" s="0">
+      <x:c r="E10">
         <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
-      <x:c r="B11" s="0" t="s">
+      <x:c r="B11" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E11" s="0" t="s">
+      <x:c r="E11" t="s">
         <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
-      <x:c r="B12" s="0">
+      <x:c r="B12">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
+      <x:c r="C12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D12" s="0" t="s">
+      <x:c r="D12" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E12" s="0">
+      <x:c r="E12">
         <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
-      <x:c r="B13" s="0">
+      <x:c r="B13">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C13" s="0" t="s">
+      <x:c r="C13" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D13" s="0" t="s">
+      <x:c r="D13" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E13" s="0" t="e">
+      <x:c r="E13" t="e">
         <x:f>SUBTOTAL(109,[Integer])</x:f>
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
-    <x:oddHeader/>
-    <x:oddFooter/>
-    <x:evenHeader/>
-    <x:evenFooter/>
-    <x:firstHeader/>
-    <x:firstFooter/>
-  </x:headerFooter>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId10"/>
   </x:tableParts>
@@ -1084,197 +1052,184 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:F13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.996339" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.424911" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11.282054" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.140625"/>
+    <x:col min="2" max="2" width="14.139196" customWidth="1"/>
+    <x:col min="3" max="3" width="11.996339" customWidth="1"/>
+    <x:col min="4" max="4" width="11.424911" customWidth="1"/>
+    <x:col min="5" max="5" width="11.282054" customWidth="1"/>
+    <x:col min="6" max="6" width="9.710625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="D2" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="E2" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
+      <x:c r="F2" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
-      <x:c r="B3" s="0">
+      <x:c r="B3">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="C3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="D3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F3" s="0">
+      <x:c r="F3">
         <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
-      <x:c r="B4" s="0">
+      <x:c r="B4">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="C4" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="D4" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F4" s="0">
+      <x:c r="F4">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
-      <x:c r="B5" s="0">
+      <x:c r="B5">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C5" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="D5" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F5" s="0">
+      <x:c r="F5">
         <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
-      <x:c r="B6" s="0">
+      <x:c r="B6">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
+      <x:c r="C6" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="D6" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="F6" s="0">
+      <x:c r="F6">
         <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
-      <x:c r="B7" s="0">
+      <x:c r="B7">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
+      <x:c r="C7" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="D7" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="F7" s="0">
+      <x:c r="F7">
         <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
-      <x:c r="B8" s="0">
+      <x:c r="B8">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
+      <x:c r="C8" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="D8" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="0">
+      <x:c r="F8">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
-      <x:c r="B9" s="0">
+      <x:c r="B9">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
+      <x:c r="C9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
+      <x:c r="D9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F9" s="0">
+      <x:c r="F9">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
-      <x:c r="B10" s="0">
+      <x:c r="B10">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C10" s="0" t="s">
+      <x:c r="C10" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D10" s="0" t="s">
+      <x:c r="D10" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="F10" s="0">
+      <x:c r="F10">
         <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
-      <x:c r="B11" s="0">
+      <x:c r="B11">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C11" s="0" t="s">
+      <x:c r="C11" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D11" s="0" t="s">
+      <x:c r="D11" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F11" s="0">
+      <x:c r="F11">
         <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
-      <x:c r="B12" s="0">
+      <x:c r="B12">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
+      <x:c r="C12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D12" s="0" t="s">
+      <x:c r="D12" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="F12" s="0">
+      <x:c r="F12">
         <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
-      <x:c r="B13" s="0" t="s">
+      <x:c r="B13" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="F13" s="0">
+      <x:c r="F13">
         <x:f>SUBTOTAL(109,[Integer])</x:f>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
-    <x:oddHeader/>
-    <x:oddFooter/>
-    <x:evenHeader/>
-    <x:evenFooter/>
-    <x:firstHeader/>
-    <x:firstFooter/>
-  </x:headerFooter>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId11"/>
   </x:tableParts>

--- a/XLibur.Tests/Resource/Examples/Tables/ResizingTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Tables/ResizingTables.xlsx
@@ -671,6 +671,7 @@
       </x:c>
       <x:c r="E13">
         <x:f>SUBTOTAL(109,[Integer])</x:f>
+        <x:v>695</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1226,6 +1227,7 @@
       </x:c>
       <x:c r="F13">
         <x:f>SUBTOTAL(109,[Integer])</x:f>
+        <x:v>695</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/XLibur.Tests/Resource/Examples/Tables/ResizingTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Tables/ResizingTables.xlsx
@@ -505,10 +505,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="14.139196" customWidth="1"/>
-    <x:col min="3" max="3" width="11.996339" customWidth="1"/>
-    <x:col min="4" max="4" width="11.424911" customWidth="1"/>
-    <x:col min="5" max="5" width="9.710625" customWidth="1"/>
+    <x:col min="2" max="2" width="13.710625" customWidth="1"/>
+    <x:col min="3" max="3" width="11.710625" customWidth="1"/>
+    <x:col min="4" max="4" width="11.139196" customWidth="1"/>
+    <x:col min="5" max="5" width="9.424911" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
@@ -688,10 +688,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="14.139196" customWidth="1"/>
-    <x:col min="3" max="3" width="11.996339" customWidth="1"/>
-    <x:col min="4" max="4" width="11.424911" customWidth="1"/>
-    <x:col min="5" max="5" width="9.710625" customWidth="1"/>
+    <x:col min="2" max="2" width="13.710625" customWidth="1"/>
+    <x:col min="3" max="3" width="11.710625" customWidth="1"/>
+    <x:col min="4" max="4" width="11.139196" customWidth="1"/>
+    <x:col min="5" max="5" width="9.424911" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
@@ -870,11 +870,11 @@
   <x:dimension ref="A1:E14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.282054" customWidth="1"/>
-    <x:col min="2" max="2" width="14.139196" customWidth="1"/>
-    <x:col min="3" max="3" width="11.996339" customWidth="1"/>
-    <x:col min="4" max="4" width="11.424911" customWidth="1"/>
-    <x:col min="5" max="5" width="9.710625" customWidth="1"/>
+    <x:col min="1" max="1" width="10.996339" customWidth="1"/>
+    <x:col min="2" max="2" width="13.710625" customWidth="1"/>
+    <x:col min="3" max="3" width="11.710625" customWidth="1"/>
+    <x:col min="4" max="4" width="11.139196" customWidth="1"/>
+    <x:col min="5" max="5" width="9.424911" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
@@ -1057,11 +1057,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="14.139196" customWidth="1"/>
-    <x:col min="3" max="3" width="11.996339" customWidth="1"/>
-    <x:col min="4" max="4" width="11.424911" customWidth="1"/>
-    <x:col min="5" max="5" width="11.282054" customWidth="1"/>
-    <x:col min="6" max="6" width="9.710625" customWidth="1"/>
+    <x:col min="2" max="2" width="13.710625" customWidth="1"/>
+    <x:col min="3" max="3" width="11.710625" customWidth="1"/>
+    <x:col min="4" max="4" width="11.139196" customWidth="1"/>
+    <x:col min="5" max="5" width="10.996339" customWidth="1"/>
+    <x:col min="6" max="6" width="9.424911" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">

--- a/XLibur.Tests/Resource/Examples/Tables/ResizingTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Tables/ResizingTables.xlsx
@@ -504,11 +504,11 @@
   <x:dimension ref="A1:E13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="13.710625" customWidth="1"/>
-    <x:col min="3" max="3" width="11.710625" customWidth="1"/>
-    <x:col min="4" max="4" width="11.139196" customWidth="1"/>
-    <x:col min="5" max="5" width="9.424911" customWidth="1"/>
+    <x:col min="1" max="1" width="9.144286"/>
+    <x:col min="2" max="2" width="13.714286" customWidth="1"/>
+    <x:col min="3" max="3" width="11.714286" customWidth="1"/>
+    <x:col min="4" max="4" width="11.142857" customWidth="1"/>
+    <x:col min="5" max="5" width="9.428571" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
@@ -687,11 +687,11 @@
   <x:dimension ref="A1:E14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="13.710625" customWidth="1"/>
-    <x:col min="3" max="3" width="11.710625" customWidth="1"/>
-    <x:col min="4" max="4" width="11.139196" customWidth="1"/>
-    <x:col min="5" max="5" width="9.424911" customWidth="1"/>
+    <x:col min="1" max="1" width="9.144286"/>
+    <x:col min="2" max="2" width="13.714286" customWidth="1"/>
+    <x:col min="3" max="3" width="11.714286" customWidth="1"/>
+    <x:col min="4" max="4" width="11.142857" customWidth="1"/>
+    <x:col min="5" max="5" width="9.428571" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
@@ -870,11 +870,11 @@
   <x:dimension ref="A1:E14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10.996339" customWidth="1"/>
-    <x:col min="2" max="2" width="13.710625" customWidth="1"/>
-    <x:col min="3" max="3" width="11.710625" customWidth="1"/>
-    <x:col min="4" max="4" width="11.139196" customWidth="1"/>
-    <x:col min="5" max="5" width="9.424911" customWidth="1"/>
+    <x:col min="1" max="1" width="11" customWidth="1"/>
+    <x:col min="2" max="2" width="13.714286" customWidth="1"/>
+    <x:col min="3" max="3" width="11.714286" customWidth="1"/>
+    <x:col min="4" max="4" width="11.142857" customWidth="1"/>
+    <x:col min="5" max="5" width="9.428571" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
@@ -1056,12 +1056,12 @@
   <x:dimension ref="A1:F13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="13.710625" customWidth="1"/>
-    <x:col min="3" max="3" width="11.710625" customWidth="1"/>
-    <x:col min="4" max="4" width="11.139196" customWidth="1"/>
-    <x:col min="5" max="5" width="10.996339" customWidth="1"/>
-    <x:col min="6" max="6" width="9.424911" customWidth="1"/>
+    <x:col min="1" max="1" width="9.144286"/>
+    <x:col min="2" max="2" width="13.714286" customWidth="1"/>
+    <x:col min="3" max="3" width="11.714286" customWidth="1"/>
+    <x:col min="4" max="4" width="11.142857" customWidth="1"/>
+    <x:col min="5" max="5" width="11" customWidth="1"/>
+    <x:col min="6" max="6" width="9.428571" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">
